--- a/RelacioniModel.xlsx
+++ b/RelacioniModel.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrade\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\faks\RII\III godina\VI semestar\Sistemi baza podataka\SBP_Projekat\SBP_Projekat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{939807BA-6D44-45D9-A0E7-B037E9D80A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDABA72-66D9-48C0-B879-BF9698D056BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AA0FC600-CBFB-4486-B246-631024553D8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>Ucenik</t>
   </si>
@@ -224,6 +224,15 @@
   </si>
   <si>
     <t>Skoslka_godina</t>
+  </si>
+  <si>
+    <t>Razred_predmet</t>
+  </si>
+  <si>
+    <t>Skolska_godina_predmet</t>
+  </si>
+  <si>
+    <t>Nastava</t>
   </si>
 </sst>
 </file>
@@ -299,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -320,6 +329,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -636,6 +649,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D644EF3A-C22D-4066-82A0-59D4BCA23514}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="E5:P65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1483,34 +1499,63 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
     </row>
-    <row r="65" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E65" t="s">
+    <row r="64" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E65" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="H65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J65" s="9"/>
+      <c r="K65" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="44" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{558E2D8F-441D-4D48-8D73-DE8E96C0242A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>